--- a/output/parana/02_base_orcamento_longa.xlsx
+++ b/output/parana/02_base_orcamento_longa.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,42 +433,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mes_ref</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mes_ano</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mes</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ano_mes_str</t>
         </is>
@@ -481,7 +493,7 @@
       <c r="D2" t="n">
         <v>4696.83</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F2" t="n">
@@ -515,7 +527,7 @@
       <c r="D3" t="n">
         <v>5157.87</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F3" t="n">
@@ -549,7 +561,7 @@
       <c r="D4" t="n">
         <v>1500.3</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F4" t="n">
@@ -583,7 +595,7 @@
       <c r="D5" t="n">
         <v>3687</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="E5" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F5" t="n">
@@ -617,7 +629,7 @@
       <c r="D6" t="n">
         <v>2470.22</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="E6" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F6" t="n">
@@ -651,7 +663,7 @@
       <c r="D7" t="n">
         <v>4008.62</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="E7" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F7" t="n">
@@ -685,7 +697,7 @@
       <c r="D8" t="n">
         <v>3511</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="E8" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F8" t="n">
@@ -719,7 +731,7 @@
       <c r="D9" t="n">
         <v>1877.65</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F9" t="n">
@@ -753,7 +765,7 @@
       <c r="D10" t="n">
         <v>1936.1</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="E10" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F10" t="n">
@@ -787,7 +799,7 @@
       <c r="D11" t="n">
         <v>3437</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F11" t="n">
@@ -821,7 +833,7 @@
       <c r="D12" t="n">
         <v>5248.06</v>
       </c>
-      <c r="E12" s="1" t="n">
+      <c r="E12" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F12" t="n">
@@ -855,7 +867,7 @@
       <c r="D13" t="n">
         <v>1990.49</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F13" t="n">
@@ -889,7 +901,7 @@
       <c r="D14" t="n">
         <v>3441</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F14" t="n">
@@ -923,7 +935,7 @@
       <c r="D15" t="n">
         <v>1606.13</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F15" t="n">
@@ -957,7 +969,7 @@
       <c r="D16" t="n">
         <v>5692.55</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F16" t="n">
@@ -991,7 +1003,7 @@
       <c r="D17" t="n">
         <v>3293</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F17" t="n">
@@ -1025,7 +1037,7 @@
       <c r="D18" t="n">
         <v>2701.74</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F18" t="n">
@@ -1059,7 +1071,7 @@
       <c r="D19" t="n">
         <v>4008.19</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F19" t="n">
@@ -1093,7 +1105,7 @@
       <c r="D20" t="n">
         <v>3889</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F20" t="n">
@@ -1127,7 +1139,7 @@
       <c r="D21" t="n">
         <v>3440.09</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="E21" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F21" t="n">
@@ -1161,7 +1173,7 @@
       <c r="D22" t="n">
         <v>4700.51</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F22" t="n">
@@ -1195,7 +1207,7 @@
       <c r="D23" t="n">
         <v>2695</v>
       </c>
-      <c r="E23" s="1" t="n">
+      <c r="E23" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F23" t="n">
@@ -1229,7 +1241,7 @@
       <c r="D24" t="n">
         <v>5071.86</v>
       </c>
-      <c r="E24" s="1" t="n">
+      <c r="E24" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F24" t="n">
@@ -1263,7 +1275,7 @@
       <c r="D25" t="n">
         <v>3886.31</v>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F25" t="n">
@@ -1297,7 +1309,7 @@
       <c r="D26" t="n">
         <v>2631</v>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F26" t="n">
@@ -1331,7 +1343,7 @@
       <c r="D27" t="n">
         <v>5341.6</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F27" t="n">
@@ -1365,7 +1377,7 @@
       <c r="D28" t="n">
         <v>2206.04</v>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F28" t="n">
@@ -1399,7 +1411,7 @@
       <c r="D29" t="n">
         <v>2493</v>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F29" t="n">
@@ -1433,7 +1445,7 @@
       <c r="D30" t="n">
         <v>2174.28</v>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F30" t="n">
@@ -1467,7 +1479,7 @@
       <c r="D31" t="n">
         <v>2810.67</v>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F31" t="n">
@@ -1501,7 +1513,7 @@
       <c r="D32" t="n">
         <v>5086</v>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F32" t="n">
@@ -1535,7 +1547,7 @@
       <c r="D33" t="n">
         <v>4689.72</v>
       </c>
-      <c r="E33" s="1" t="n">
+      <c r="E33" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F33" t="n">
@@ -1569,7 +1581,7 @@
       <c r="D34" t="n">
         <v>5664.17</v>
       </c>
-      <c r="E34" s="1" t="n">
+      <c r="E34" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F34" t="n">
@@ -1603,7 +1615,7 @@
       <c r="D35" t="n">
         <v>6838</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F35" t="n">
@@ -1637,7 +1649,7 @@
       <c r="D36" t="n">
         <v>2119.59</v>
       </c>
-      <c r="E36" s="1" t="n">
+      <c r="E36" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F36" t="n">
@@ -1671,7 +1683,7 @@
       <c r="D37" t="n">
         <v>4352.03</v>
       </c>
-      <c r="E37" s="1" t="n">
+      <c r="E37" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F37" t="n">
@@ -1705,7 +1717,7 @@
       <c r="D38" t="n">
         <v>2552.83</v>
       </c>
-      <c r="E38" s="1" t="n">
+      <c r="E38" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F38" t="n">
@@ -1739,7 +1751,7 @@
       <c r="D39" t="n">
         <v>5271.87</v>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F39" t="n">
@@ -1773,7 +1785,7 @@
       <c r="D40" t="n">
         <v>4374.3</v>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="F40" t="n">
@@ -1807,7 +1819,7 @@
       <c r="D41" t="n">
         <v>2373</v>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F41" t="n">
@@ -1841,7 +1853,7 @@
       <c r="D42" t="n">
         <v>3676.22</v>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F42" t="n">
@@ -1875,7 +1887,7 @@
       <c r="D43" t="n">
         <v>1748.62</v>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="F43" t="n">
@@ -1909,7 +1921,7 @@
       <c r="D44" t="n">
         <v>3691</v>
       </c>
-      <c r="E44" s="1" t="n">
+      <c r="E44" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F44" t="n">
@@ -1943,7 +1955,7 @@
       <c r="D45" t="n">
         <v>2137.65</v>
       </c>
-      <c r="E45" s="1" t="n">
+      <c r="E45" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F45" t="n">
@@ -1977,7 +1989,7 @@
       <c r="D46" t="n">
         <v>4222.1</v>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="F46" t="n">
@@ -2011,7 +2023,7 @@
       <c r="D47" t="n">
         <v>3711</v>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F47" t="n">
@@ -2045,7 +2057,7 @@
       <c r="D48" t="n">
         <v>4776.06</v>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F48" t="n">
@@ -2079,7 +2091,7 @@
       <c r="D49" t="n">
         <v>1638.49</v>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="F49" t="n">
@@ -2113,7 +2125,7 @@
       <c r="D50" t="n">
         <v>1977</v>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F50" t="n">
@@ -2147,7 +2159,7 @@
       <c r="D51" t="n">
         <v>5416.13</v>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F51" t="n">
@@ -2181,7 +2193,7 @@
       <c r="D52" t="n">
         <v>5018.55</v>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="F52" t="n">
@@ -2215,7 +2227,7 @@
       <c r="D53" t="n">
         <v>3805</v>
       </c>
-      <c r="E53" s="1" t="n">
+      <c r="E53" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F53" t="n">
@@ -2249,7 +2261,7 @@
       <c r="D54" t="n">
         <v>1505.74</v>
       </c>
-      <c r="E54" s="1" t="n">
+      <c r="E54" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F54" t="n">
@@ -2283,7 +2295,7 @@
       <c r="D55" t="n">
         <v>2294.19</v>
       </c>
-      <c r="E55" s="1" t="n">
+      <c r="E55" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="F55" t="n">
@@ -2317,7 +2329,7 @@
       <c r="D56" t="n">
         <v>2783</v>
       </c>
-      <c r="E56" s="1" t="n">
+      <c r="E56" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F56" t="n">
@@ -2351,7 +2363,7 @@
       <c r="D57" t="n">
         <v>2648.09</v>
       </c>
-      <c r="E57" s="1" t="n">
+      <c r="E57" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F57" t="n">
@@ -2385,7 +2397,7 @@
       <c r="D58" t="n">
         <v>4400.51</v>
       </c>
-      <c r="E58" s="1" t="n">
+      <c r="E58" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="F58" t="n">
@@ -2419,7 +2431,7 @@
       <c r="D59" t="n">
         <v>3327</v>
       </c>
-      <c r="E59" s="1" t="n">
+      <c r="E59" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F59" t="n">
@@ -2453,7 +2465,7 @@
       <c r="D60" t="n">
         <v>4661.86</v>
       </c>
-      <c r="E60" s="1" t="n">
+      <c r="E60" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F60" t="n">
@@ -2487,7 +2499,7 @@
       <c r="D61" t="n">
         <v>3178.31</v>
       </c>
-      <c r="E61" s="1" t="n">
+      <c r="E61" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="F61" t="n">
@@ -2521,7 +2533,7 @@
       <c r="D62" t="n">
         <v>3377</v>
       </c>
-      <c r="E62" s="1" t="n">
+      <c r="E62" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F62" t="n">
@@ -2555,7 +2567,7 @@
       <c r="D63" t="n">
         <v>3463.6</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F63" t="n">
@@ -2589,7 +2601,7 @@
       <c r="D64" t="n">
         <v>3204.04</v>
       </c>
-      <c r="E64" s="1" t="n">
+      <c r="E64" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="F64" t="n">
@@ -2623,7 +2635,7 @@
       <c r="D65" t="n">
         <v>5713</v>
       </c>
-      <c r="E65" s="1" t="n">
+      <c r="E65" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F65" t="n">
@@ -2657,7 +2669,7 @@
       <c r="D66" t="n">
         <v>4210.28</v>
       </c>
-      <c r="E66" s="1" t="n">
+      <c r="E66" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F66" t="n">
@@ -2691,7 +2703,7 @@
       <c r="D67" t="n">
         <v>5822.67</v>
       </c>
-      <c r="E67" s="1" t="n">
+      <c r="E67" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="F67" t="n">
@@ -2725,7 +2737,7 @@
       <c r="D68" t="n">
         <v>3156</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E68" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F68" t="n">
@@ -2759,7 +2771,7 @@
       <c r="D69" t="n">
         <v>4351.72</v>
       </c>
-      <c r="E69" s="1" t="n">
+      <c r="E69" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F69" t="n">
@@ -2793,7 +2805,7 @@
       <c r="D70" t="n">
         <v>3160.17</v>
       </c>
-      <c r="E70" s="1" t="n">
+      <c r="E70" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="F70" t="n">
@@ -2827,7 +2839,7 @@
       <c r="D71" t="n">
         <v>6852</v>
       </c>
-      <c r="E71" s="1" t="n">
+      <c r="E71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F71" t="n">
@@ -2861,7 +2873,7 @@
       <c r="D72" t="n">
         <v>4325.59</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F72" t="n">
@@ -2895,7 +2907,7 @@
       <c r="D73" t="n">
         <v>5124.03</v>
       </c>
-      <c r="E73" s="1" t="n">
+      <c r="E73" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="F73" t="n">
